--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,840 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124755299</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>320768</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6432130</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spår av födosökande spillkråka</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124755223</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>320785</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6432135</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124755468</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>320972</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6432197</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår av födosökande spillkråka</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124755096</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>320800</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6432124</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124755006</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>320828</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6432213</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124755376</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>320790</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6432140</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124754215</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>320805</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6432195</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755299</v>
+        <v>124754215</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -828,16 +828,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320768</v>
+        <v>320805</v>
       </c>
       <c r="R3" t="n">
-        <v>6432130</v>
+        <v>6432195</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,14 +876,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +903,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755223</v>
+        <v>124755299</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +957,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320785</v>
+        <v>320768</v>
       </c>
       <c r="R4" t="n">
-        <v>6432135</v>
+        <v>6432130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1271,7 +1272,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755006</v>
+        <v>124755376</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320828</v>
+        <v>320790</v>
       </c>
       <c r="R7" t="n">
-        <v>6432213</v>
+        <v>6432140</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1364,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,7 +1391,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755376</v>
+        <v>124755006</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1442,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320790</v>
+        <v>320828</v>
       </c>
       <c r="R8" t="n">
-        <v>6432140</v>
+        <v>6432213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1483,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124754215</v>
+        <v>124755223</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,33 +1522,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1557,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320805</v>
+        <v>320785</v>
       </c>
       <c r="R9" t="n">
-        <v>6432195</v>
+        <v>6432135</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,19 +1595,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,12 +1617,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754215</v>
+        <v>124755223</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,33 +807,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -843,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320805</v>
+        <v>320785</v>
       </c>
       <c r="R3" t="n">
-        <v>6432195</v>
+        <v>6432135</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,19 +880,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,19 +902,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755299</v>
+        <v>124755468</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -967,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320768</v>
+        <v>320972</v>
       </c>
       <c r="R4" t="n">
-        <v>6432130</v>
+        <v>6432197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755468</v>
+        <v>124754215</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1067,16 +1066,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1086,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320972</v>
+        <v>320805</v>
       </c>
       <c r="R5" t="n">
-        <v>6432197</v>
+        <v>6432195</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,14 +1114,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755096</v>
+        <v>124755299</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,25 +1165,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320800</v>
+        <v>320768</v>
       </c>
       <c r="R6" t="n">
-        <v>6432124</v>
+        <v>6432130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,7 +1272,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755376</v>
+        <v>124755096</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320790</v>
+        <v>320800</v>
       </c>
       <c r="R7" t="n">
-        <v>6432140</v>
+        <v>6432124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1510,7 +1510,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755223</v>
+        <v>124755376</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320785</v>
+        <v>320790</v>
       </c>
       <c r="R9" t="n">
-        <v>6432135</v>
+        <v>6432140</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,6 +1627,240 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124879118</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>320897</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6432269</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124877800</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>321049</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6432311</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755223</v>
+        <v>124755468</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320785</v>
+        <v>320972</v>
       </c>
       <c r="R3" t="n">
-        <v>6432135</v>
+        <v>6432197</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755468</v>
+        <v>124755096</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320972</v>
+        <v>320800</v>
       </c>
       <c r="R4" t="n">
-        <v>6432197</v>
+        <v>6432124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754215</v>
+        <v>124755299</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1066,12 +1066,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1081,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320805</v>
+        <v>320768</v>
       </c>
       <c r="R5" t="n">
-        <v>6432195</v>
+        <v>6432130</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,19 +1118,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,22 +1140,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755299</v>
+        <v>124755223</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,25 +1164,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1195,7 +1194,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1205,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320768</v>
+        <v>320785</v>
       </c>
       <c r="R6" t="n">
-        <v>6432130</v>
+        <v>6432135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755096</v>
+        <v>124755376</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320800</v>
+        <v>320790</v>
       </c>
       <c r="R7" t="n">
-        <v>6432124</v>
+        <v>6432140</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1363,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755006</v>
+        <v>124754215</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,37 +1402,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1443,13 +1438,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320828</v>
+        <v>320805</v>
       </c>
       <c r="R8" t="n">
-        <v>6432213</v>
+        <v>6432195</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,14 +1471,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,19 +1498,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755376</v>
+        <v>124755006</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320790</v>
+        <v>320828</v>
       </c>
       <c r="R9" t="n">
-        <v>6432140</v>
+        <v>6432213</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879118</v>
+        <v>124877800</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1662,7 +1662,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1677,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>320897</v>
+        <v>321049</v>
       </c>
       <c r="R10" t="n">
-        <v>6432269</v>
+        <v>6432311</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,19 +1714,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,7 +1743,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124877800</v>
+        <v>124879118</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1782,11 +1776,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1801,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321049</v>
+        <v>320897</v>
       </c>
       <c r="R11" t="n">
-        <v>6432311</v>
+        <v>6432269</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1834,9 +1824,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755468</v>
+        <v>124755376</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320972</v>
+        <v>320790</v>
       </c>
       <c r="R3" t="n">
-        <v>6432197</v>
+        <v>6432140</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755096</v>
+        <v>124755299</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320800</v>
+        <v>320768</v>
       </c>
       <c r="R4" t="n">
-        <v>6432124</v>
+        <v>6432130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755299</v>
+        <v>124755468</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320768</v>
+        <v>320972</v>
       </c>
       <c r="R5" t="n">
-        <v>6432130</v>
+        <v>6432197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755376</v>
+        <v>124754215</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,37 +1283,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1323,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320790</v>
+        <v>320805</v>
       </c>
       <c r="R7" t="n">
-        <v>6432140</v>
+        <v>6432195</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,14 +1352,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124754215</v>
+        <v>124755006</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,33 +1403,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1438,13 +1443,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320805</v>
+        <v>320828</v>
       </c>
       <c r="R8" t="n">
-        <v>6432195</v>
+        <v>6432213</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,19 +1476,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,19 +1498,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755006</v>
+        <v>124755096</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320828</v>
+        <v>320800</v>
       </c>
       <c r="R9" t="n">
-        <v>6432213</v>
+        <v>6432124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755376</v>
+        <v>124754215</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,37 +807,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320790</v>
+        <v>320805</v>
       </c>
       <c r="R3" t="n">
-        <v>6432140</v>
+        <v>6432195</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,14 +876,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +903,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755299</v>
+        <v>124755376</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +927,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +957,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320768</v>
+        <v>320790</v>
       </c>
       <c r="R4" t="n">
-        <v>6432130</v>
+        <v>6432140</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1152,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755223</v>
+        <v>124755299</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1165,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1194,7 +1195,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1204,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320785</v>
+        <v>320768</v>
       </c>
       <c r="R6" t="n">
-        <v>6432135</v>
+        <v>6432130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1245,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124754215</v>
+        <v>124755223</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,33 +1284,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1319,13 +1324,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320805</v>
+        <v>320785</v>
       </c>
       <c r="R7" t="n">
-        <v>6432195</v>
+        <v>6432135</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,19 +1357,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,19 +1379,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755006</v>
+        <v>124755096</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320828</v>
+        <v>320800</v>
       </c>
       <c r="R8" t="n">
-        <v>6432213</v>
+        <v>6432124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,7 +1510,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755096</v>
+        <v>124755006</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320800</v>
+        <v>320828</v>
       </c>
       <c r="R9" t="n">
-        <v>6432124</v>
+        <v>6432213</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124877800</v>
+        <v>124879118</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1662,11 +1662,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1681,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321049</v>
+        <v>320897</v>
       </c>
       <c r="R10" t="n">
-        <v>6432311</v>
+        <v>6432269</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1714,9 +1710,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,7 +1749,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124879118</v>
+        <v>124877800</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1776,7 +1782,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1791,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320897</v>
+        <v>321049</v>
       </c>
       <c r="R11" t="n">
-        <v>6432269</v>
+        <v>6432311</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1824,19 +1834,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754215</v>
+        <v>124755006</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,33 +807,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -843,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320805</v>
+        <v>320828</v>
       </c>
       <c r="R3" t="n">
-        <v>6432195</v>
+        <v>6432213</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,19 +880,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755376</v>
+        <v>124755299</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,7 +956,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320790</v>
+        <v>320768</v>
       </c>
       <c r="R4" t="n">
-        <v>6432140</v>
+        <v>6432130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1153,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755299</v>
+        <v>124755096</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,25 +1164,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1195,7 +1194,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1205,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320768</v>
+        <v>320800</v>
       </c>
       <c r="R6" t="n">
-        <v>6432130</v>
+        <v>6432124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755223</v>
+        <v>124754215</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,37 +1283,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1324,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320785</v>
+        <v>320805</v>
       </c>
       <c r="R7" t="n">
-        <v>6432135</v>
+        <v>6432195</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,14 +1352,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,19 +1379,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755096</v>
+        <v>124755223</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320800</v>
+        <v>320785</v>
       </c>
       <c r="R8" t="n">
-        <v>6432124</v>
+        <v>6432135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,7 +1510,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755006</v>
+        <v>124755376</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320828</v>
+        <v>320790</v>
       </c>
       <c r="R9" t="n">
-        <v>6432213</v>
+        <v>6432140</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755006</v>
+        <v>124755468</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320828</v>
+        <v>320972</v>
       </c>
       <c r="R3" t="n">
-        <v>6432213</v>
+        <v>6432197</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755299</v>
+        <v>124755006</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320768</v>
+        <v>320828</v>
       </c>
       <c r="R4" t="n">
-        <v>6432130</v>
+        <v>6432213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755468</v>
+        <v>124755096</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,25 +1045,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320972</v>
+        <v>320800</v>
       </c>
       <c r="R5" t="n">
-        <v>6432197</v>
+        <v>6432124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755096</v>
+        <v>124755376</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320800</v>
+        <v>320790</v>
       </c>
       <c r="R6" t="n">
-        <v>6432124</v>
+        <v>6432140</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1510,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755376</v>
+        <v>124755299</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,25 +1522,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1552,7 +1552,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320790</v>
+        <v>320768</v>
       </c>
       <c r="R9" t="n">
-        <v>6432140</v>
+        <v>6432130</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879118</v>
+        <v>124879054</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755006</v>
+        <v>124755096</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320828</v>
+        <v>320800</v>
       </c>
       <c r="R4" t="n">
-        <v>6432213</v>
+        <v>6432124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755096</v>
+        <v>124755006</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320800</v>
+        <v>320828</v>
       </c>
       <c r="R5" t="n">
-        <v>6432124</v>
+        <v>6432213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755376</v>
+        <v>124755299</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1164,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1194,7 +1194,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320790</v>
+        <v>320768</v>
       </c>
       <c r="R6" t="n">
-        <v>6432140</v>
+        <v>6432130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124754215</v>
+        <v>124755376</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,33 +1283,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1319,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320805</v>
+        <v>320790</v>
       </c>
       <c r="R7" t="n">
-        <v>6432195</v>
+        <v>6432140</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,19 +1356,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,22 +1378,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755223</v>
+        <v>124754215</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,37 +1402,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1443,13 +1438,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320785</v>
+        <v>320805</v>
       </c>
       <c r="R8" t="n">
-        <v>6432135</v>
+        <v>6432195</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,14 +1471,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,22 +1498,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755299</v>
+        <v>124755223</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,25 +1522,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1552,7 +1552,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320768</v>
+        <v>320785</v>
       </c>
       <c r="R9" t="n">
-        <v>6432130</v>
+        <v>6432135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879054</v>
+        <v>124877800</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1662,7 +1662,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1677,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>320897</v>
+        <v>321049</v>
       </c>
       <c r="R10" t="n">
-        <v>6432269</v>
+        <v>6432311</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,19 +1714,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,7 +1743,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124877800</v>
+        <v>124879118</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1782,11 +1776,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1801,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321049</v>
+        <v>320897</v>
       </c>
       <c r="R11" t="n">
-        <v>6432311</v>
+        <v>6432269</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1834,9 +1824,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1390,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124754215</v>
+        <v>124755223</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,33 +1402,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1438,13 +1442,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320805</v>
+        <v>320785</v>
       </c>
       <c r="R8" t="n">
-        <v>6432195</v>
+        <v>6432135</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,19 +1475,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,22 +1497,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755223</v>
+        <v>124754215</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,37 +1521,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1562,13 +1557,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320785</v>
+        <v>320805</v>
       </c>
       <c r="R9" t="n">
-        <v>6432135</v>
+        <v>6432195</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1595,14 +1590,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,12 +1617,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755468</v>
+        <v>124755096</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320972</v>
+        <v>320800</v>
       </c>
       <c r="R3" t="n">
-        <v>6432197</v>
+        <v>6432124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755096</v>
+        <v>124755468</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320800</v>
+        <v>320972</v>
       </c>
       <c r="R4" t="n">
-        <v>6432124</v>
+        <v>6432197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755006</v>
+        <v>124754215</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,37 +1045,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1085,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320828</v>
+        <v>320805</v>
       </c>
       <c r="R5" t="n">
-        <v>6432213</v>
+        <v>6432195</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,14 +1114,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,12 +1141,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1390,7 +1391,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755223</v>
+        <v>124755006</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1442,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320785</v>
+        <v>320828</v>
       </c>
       <c r="R8" t="n">
-        <v>6432135</v>
+        <v>6432213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1483,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124754215</v>
+        <v>124755223</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,33 +1522,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1557,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320805</v>
+        <v>320785</v>
       </c>
       <c r="R9" t="n">
-        <v>6432195</v>
+        <v>6432135</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,19 +1595,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,12 +1617,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755096</v>
+        <v>124755223</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320800</v>
+        <v>320785</v>
       </c>
       <c r="R3" t="n">
-        <v>6432124</v>
+        <v>6432135</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755468</v>
+        <v>124755299</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320972</v>
+        <v>320768</v>
       </c>
       <c r="R4" t="n">
-        <v>6432197</v>
+        <v>6432130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754215</v>
+        <v>124755376</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,33 +1045,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1081,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320805</v>
+        <v>320790</v>
       </c>
       <c r="R5" t="n">
-        <v>6432195</v>
+        <v>6432140</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,19 +1118,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,19 +1140,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755299</v>
+        <v>124755468</v>
       </c>
       <c r="B6" t="n">
         <v>57529</v>
@@ -1205,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320768</v>
+        <v>320972</v>
       </c>
       <c r="R6" t="n">
-        <v>6432130</v>
+        <v>6432197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755376</v>
+        <v>124754215</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,37 +1283,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1324,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320790</v>
+        <v>320805</v>
       </c>
       <c r="R7" t="n">
-        <v>6432140</v>
+        <v>6432195</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,14 +1352,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,12 +1379,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755223</v>
+        <v>124755096</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320785</v>
+        <v>320800</v>
       </c>
       <c r="R9" t="n">
-        <v>6432135</v>
+        <v>6432124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124877800</v>
+        <v>124879118</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1662,11 +1662,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1681,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321049</v>
+        <v>320897</v>
       </c>
       <c r="R10" t="n">
-        <v>6432311</v>
+        <v>6432269</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1714,9 +1710,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,7 +1749,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124879118</v>
+        <v>124877800</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1776,7 +1782,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1791,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320897</v>
+        <v>321049</v>
       </c>
       <c r="R11" t="n">
-        <v>6432269</v>
+        <v>6432311</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1824,19 +1834,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755223</v>
+        <v>124755096</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320785</v>
+        <v>320800</v>
       </c>
       <c r="R3" t="n">
-        <v>6432135</v>
+        <v>6432124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755376</v>
+        <v>124755468</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,25 +1045,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320790</v>
+        <v>320972</v>
       </c>
       <c r="R5" t="n">
-        <v>6432140</v>
+        <v>6432197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755468</v>
+        <v>124755223</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1164,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1194,7 +1194,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320972</v>
+        <v>320785</v>
       </c>
       <c r="R6" t="n">
-        <v>6432197</v>
+        <v>6432135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1391,7 +1391,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755006</v>
+        <v>124755376</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320828</v>
+        <v>320790</v>
       </c>
       <c r="R8" t="n">
-        <v>6432213</v>
+        <v>6432140</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,7 +1510,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755096</v>
+        <v>124755006</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320800</v>
+        <v>320828</v>
       </c>
       <c r="R9" t="n">
-        <v>6432124</v>
+        <v>6432213</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879118</v>
+        <v>124877800</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1662,7 +1662,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1677,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>320897</v>
+        <v>321049</v>
       </c>
       <c r="R10" t="n">
-        <v>6432269</v>
+        <v>6432311</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,19 +1714,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,7 +1743,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124877800</v>
+        <v>124879054</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1782,11 +1776,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1801,10 +1791,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321049</v>
+        <v>320897</v>
       </c>
       <c r="R11" t="n">
-        <v>6432311</v>
+        <v>6432269</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1834,9 +1824,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -675,58 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124502379</v>
+        <v>124755299</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320975</v>
+        <v>320768</v>
       </c>
       <c r="R2" t="n">
-        <v>6432251</v>
+        <v>6432130</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,22 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755096</v>
+        <v>124754215</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,37 +806,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320800</v>
+        <v>320805</v>
       </c>
       <c r="R3" t="n">
-        <v>6432124</v>
+        <v>6432195</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,14 +875,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,19 +902,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755299</v>
+        <v>124755468</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320768</v>
+        <v>320972</v>
       </c>
       <c r="R4" t="n">
-        <v>6432130</v>
+        <v>6432197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1033,49 +1033,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755468</v>
+        <v>124879118</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1085,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320972</v>
+        <v>320897</v>
       </c>
       <c r="R5" t="n">
-        <v>6432197</v>
+        <v>6432269</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,14 +1114,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,26 +1141,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755223</v>
+        <v>124502379</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1185,29 +1186,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320785</v>
+        <v>320975</v>
       </c>
       <c r="R6" t="n">
-        <v>6432135</v>
+        <v>6432251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,17 +1231,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,57 +1261,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124754215</v>
+        <v>124755096</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1319,13 +1325,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320805</v>
+        <v>320800</v>
       </c>
       <c r="R7" t="n">
-        <v>6432195</v>
+        <v>6432124</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,19 +1358,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,26 +1380,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755376</v>
+        <v>124755006</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1443,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320790</v>
+        <v>320828</v>
       </c>
       <c r="R8" t="n">
-        <v>6432140</v>
+        <v>6432213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,7 +1484,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,14 +1511,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755006</v>
+        <v>124877800</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1562,13 +1563,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320828</v>
+        <v>321049</v>
       </c>
       <c r="R9" t="n">
-        <v>6432213</v>
+        <v>6432311</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1598,11 +1599,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,26 +1613,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124877800</v>
+        <v>124755223</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1681,13 +1677,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321049</v>
+        <v>320785</v>
       </c>
       <c r="R10" t="n">
-        <v>6432311</v>
+        <v>6432135</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,6 +1713,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,26 +1732,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124879054</v>
+        <v>124755376</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1776,7 +1777,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1791,13 +1796,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320897</v>
+        <v>320790</v>
       </c>
       <c r="R11" t="n">
-        <v>6432269</v>
+        <v>6432140</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1824,19 +1829,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124755299</v>
+        <v>124754215</v>
       </c>
       <c r="B2" t="n">
         <v>57529</v>
@@ -708,16 +708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320768</v>
+        <v>320805</v>
       </c>
       <c r="R2" t="n">
-        <v>6432130</v>
+        <v>6432195</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,14 +756,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,19 +783,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754215</v>
+        <v>124755299</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -827,12 +828,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320805</v>
+        <v>320768</v>
       </c>
       <c r="R3" t="n">
-        <v>6432195</v>
+        <v>6432130</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,19 +880,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +902,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1033,14 +1033,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879118</v>
+        <v>124755376</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1066,7 +1066,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1081,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320897</v>
+        <v>320790</v>
       </c>
       <c r="R5" t="n">
-        <v>6432269</v>
+        <v>6432140</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,19 +1118,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,19 +1140,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124502379</v>
+        <v>124877800</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1186,28 +1185,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320975</v>
+        <v>321049</v>
       </c>
       <c r="R6" t="n">
-        <v>6432251</v>
+        <v>6432311</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,22 +1234,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,12 +1254,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1392,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755006</v>
+        <v>124755223</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1444,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320828</v>
+        <v>320785</v>
       </c>
       <c r="R8" t="n">
-        <v>6432213</v>
+        <v>6432135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1477,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124877800</v>
+        <v>124502379</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1544,32 +1537,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321049</v>
+        <v>320975</v>
       </c>
       <c r="R9" t="n">
-        <v>6432311</v>
+        <v>6432251</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1593,12 +1582,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,19 +1612,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124755223</v>
+        <v>124755006</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1677,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>320785</v>
+        <v>320828</v>
       </c>
       <c r="R10" t="n">
-        <v>6432135</v>
+        <v>6432213</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,7 +1716,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,14 +1743,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124755376</v>
+        <v>124879118</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1777,11 +1776,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1796,13 +1791,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320790</v>
+        <v>320897</v>
       </c>
       <c r="R11" t="n">
-        <v>6432140</v>
+        <v>6432269</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1829,14 +1824,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124754215</v>
+        <v>124755468</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,12 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320805</v>
+        <v>320972</v>
       </c>
       <c r="R2" t="n">
-        <v>6432195</v>
+        <v>6432197</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,19 +760,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,22 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124755299</v>
+        <v>124754215</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,16 +827,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320768</v>
+        <v>320805</v>
       </c>
       <c r="R3" t="n">
-        <v>6432130</v>
+        <v>6432195</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,14 +875,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755468</v>
+        <v>124755299</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320972</v>
+        <v>320768</v>
       </c>
       <c r="R4" t="n">
-        <v>6432197</v>
+        <v>6432130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1033,14 +1033,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755376</v>
+        <v>124879118</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1066,11 +1066,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1085,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320790</v>
+        <v>320897</v>
       </c>
       <c r="R5" t="n">
-        <v>6432140</v>
+        <v>6432269</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,14 +1114,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,26 +1141,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124877800</v>
+        <v>124755376</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1204,13 +1205,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321049</v>
+        <v>320790</v>
       </c>
       <c r="R6" t="n">
-        <v>6432311</v>
+        <v>6432140</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,6 +1241,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,22 +1260,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755096</v>
+        <v>124877800</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1318,13 +1324,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320800</v>
+        <v>321049</v>
       </c>
       <c r="R7" t="n">
-        <v>6432124</v>
+        <v>6432311</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,11 +1360,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,22 +1374,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755223</v>
+        <v>124755006</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320785</v>
+        <v>320828</v>
       </c>
       <c r="R8" t="n">
-        <v>6432135</v>
+        <v>6432213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1478,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124502379</v>
+        <v>124755223</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,25 +1538,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320975</v>
+        <v>320785</v>
       </c>
       <c r="R9" t="n">
-        <v>6432251</v>
+        <v>6432135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,22 +1587,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,22 +1612,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124755006</v>
+        <v>124755096</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>320828</v>
+        <v>320800</v>
       </c>
       <c r="R10" t="n">
-        <v>6432213</v>
+        <v>6432124</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124879118</v>
+        <v>124502379</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,23 +1781,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320897</v>
+        <v>320975</v>
       </c>
       <c r="R11" t="n">
-        <v>6432269</v>
+        <v>6432251</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,22 +1821,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124755468</v>
+        <v>124755299</v>
       </c>
       <c r="B2" t="n">
         <v>57632</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320972</v>
+        <v>320768</v>
       </c>
       <c r="R2" t="n">
-        <v>6432197</v>
+        <v>6432130</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755299</v>
+        <v>124755468</v>
       </c>
       <c r="B4" t="n">
         <v>57632</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320768</v>
+        <v>320972</v>
       </c>
       <c r="R4" t="n">
-        <v>6432130</v>
+        <v>6432197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879118</v>
+        <v>124755096</v>
       </c>
       <c r="B5" t="n">
         <v>56836</v>
@@ -1066,7 +1066,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1081,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320897</v>
+        <v>320800</v>
       </c>
       <c r="R5" t="n">
-        <v>6432269</v>
+        <v>6432124</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,19 +1118,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,12 +1140,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1272,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124877800</v>
+        <v>124755006</v>
       </c>
       <c r="B7" t="n">
         <v>56836</v>
@@ -1324,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321049</v>
+        <v>320828</v>
       </c>
       <c r="R7" t="n">
-        <v>6432311</v>
+        <v>6432213</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,6 +1359,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,19 +1378,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755006</v>
+        <v>124755223</v>
       </c>
       <c r="B8" t="n">
         <v>56836</v>
@@ -1438,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320828</v>
+        <v>320785</v>
       </c>
       <c r="R8" t="n">
-        <v>6432213</v>
+        <v>6432135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1482,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755223</v>
+        <v>124879118</v>
       </c>
       <c r="B9" t="n">
         <v>56836</v>
@@ -1538,11 +1542,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320785</v>
+        <v>320897</v>
       </c>
       <c r="R9" t="n">
-        <v>6432135</v>
+        <v>6432269</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,14 +1590,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,19 +1617,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124755096</v>
+        <v>124502379</v>
       </c>
       <c r="B10" t="n">
         <v>56836</v>
@@ -1657,29 +1662,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>320800</v>
+        <v>320975</v>
       </c>
       <c r="R10" t="n">
-        <v>6432124</v>
+        <v>6432251</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,17 +1707,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,19 +1737,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124502379</v>
+        <v>124877800</v>
       </c>
       <c r="B11" t="n">
         <v>56836</v>
@@ -1776,28 +1782,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320975</v>
+        <v>321049</v>
       </c>
       <c r="R11" t="n">
-        <v>6432251</v>
+        <v>6432311</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,22 +1831,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1033,15 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124755096</v>
+        <v>124879118</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,11 +1061,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1085,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320800</v>
+        <v>320897</v>
       </c>
       <c r="R5" t="n">
-        <v>6432124</v>
+        <v>6432269</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,14 +1109,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,27 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124755376</v>
+        <v>124502379</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,29 +1176,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320790</v>
+        <v>320975</v>
       </c>
       <c r="R6" t="n">
-        <v>6432140</v>
+        <v>6432251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,17 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,12 +1251,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1274,12 +1266,7 @@
         <v>124755006</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,15 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755223</v>
+        <v>124755376</v>
       </c>
       <c r="B8" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320785</v>
+        <v>320790</v>
       </c>
       <c r="R8" t="n">
-        <v>6432135</v>
+        <v>6432140</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1464,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,15 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124879118</v>
+        <v>124755096</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1519,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
@@ -1557,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320897</v>
+        <v>320800</v>
       </c>
       <c r="R9" t="n">
-        <v>6432269</v>
+        <v>6432124</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,19 +1571,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:48</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,27 +1593,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124502379</v>
+        <v>124877800</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,28 +1633,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>320975</v>
+        <v>321049</v>
       </c>
       <c r="R10" t="n">
-        <v>6432251</v>
+        <v>6432311</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,22 +1682,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,27 +1702,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124877800</v>
+        <v>124755223</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,13 +1761,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321049</v>
+        <v>320785</v>
       </c>
       <c r="R11" t="n">
-        <v>6432311</v>
+        <v>6432135</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,6 +1797,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,12 +1816,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1033,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879118</v>
+        <v>124502379</v>
       </c>
       <c r="B5" t="n">
         <v>56843</v>
@@ -1066,23 +1066,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320897</v>
+        <v>320975</v>
       </c>
       <c r="R5" t="n">
-        <v>6432269</v>
+        <v>6432251</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1106,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,19 +1136,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124502379</v>
+        <v>124879118</v>
       </c>
       <c r="B6" t="n">
         <v>56843</v>
@@ -1181,23 +1181,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320975</v>
+        <v>320897</v>
       </c>
       <c r="R6" t="n">
-        <v>6432251</v>
+        <v>6432269</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,12 +1251,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1033,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124502379</v>
+        <v>124879118</v>
       </c>
       <c r="B5" t="n">
         <v>56843</v>
@@ -1066,23 +1066,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320975</v>
+        <v>320897</v>
       </c>
       <c r="R5" t="n">
-        <v>6432251</v>
+        <v>6432269</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1106,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,19 +1136,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124879118</v>
+        <v>124502379</v>
       </c>
       <c r="B6" t="n">
         <v>56843</v>
@@ -1181,23 +1181,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320897</v>
+        <v>320975</v>
       </c>
       <c r="R6" t="n">
-        <v>6432269</v>
+        <v>6432251</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,12 +1251,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1826,6 +1826,216 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131917439</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58063</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>320830</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6432232</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131917572</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57092</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>321033</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6432350</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,6 +2036,566 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132009630</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartedalen, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>320875</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6432213</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stor kudde mes blåmossa, ca 40x60cm</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132011429</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartedalen, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>320970</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6432204</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132010885</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96636</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartedalen, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>320970</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6432204</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stööre kudde 30×40</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132012912</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartedalen, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>321109</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6432420</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132009686</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartedalen, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>320890</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6432241</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1831,7 +1831,7 @@
         <v>131917439</v>
       </c>
       <c r="B12" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131917572</v>
       </c>
       <c r="B13" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>132009630</v>
       </c>
       <c r="B14" t="n">
-        <v>96636</v>
+        <v>96637</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>132011429</v>
       </c>
       <c r="B15" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132010885</v>
       </c>
       <c r="B16" t="n">
-        <v>96636</v>
+        <v>96637</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>132012912</v>
       </c>
       <c r="B17" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>132009686</v>
       </c>
       <c r="B18" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1831,7 +1831,7 @@
         <v>131917439</v>
       </c>
       <c r="B12" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131917572</v>
       </c>
       <c r="B13" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>132009630</v>
       </c>
       <c r="B14" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>132011429</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132010885</v>
       </c>
       <c r="B16" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>132012912</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>132009686</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1831,7 +1831,7 @@
         <v>131917439</v>
       </c>
       <c r="B12" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131917572</v>
       </c>
       <c r="B13" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>132009630</v>
       </c>
       <c r="B14" t="n">
-        <v>96642</v>
+        <v>96644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2150,40 +2150,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132011429</v>
+        <v>132010885</v>
       </c>
       <c r="B15" t="n">
-        <v>57909</v>
+        <v>96644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartedalen, Svartedalen, Boh</t>
@@ -2196,7 +2191,7 @@
         <v>6432204</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2225,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2230,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stööre kudde 30×40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,48 +2262,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132010885</v>
+        <v>132012912</v>
       </c>
       <c r="B16" t="n">
-        <v>96642</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>320970</v>
+        <v>321109</v>
       </c>
       <c r="R16" t="n">
-        <v>6432204</v>
+        <v>6432420</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2327,27 +2332,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stööre kudde 30×40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132012912</v>
+        <v>132009686</v>
       </c>
       <c r="B17" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321109</v>
+        <v>320890</v>
       </c>
       <c r="R17" t="n">
-        <v>6432420</v>
+        <v>6432241</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2444,22 +2444,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,10 +2486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132009686</v>
+        <v>132011429</v>
       </c>
       <c r="B18" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>320890</v>
+        <v>320970</v>
       </c>
       <c r="R18" t="n">
-        <v>6432241</v>
+        <v>6432204</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -2150,48 +2150,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132010885</v>
+        <v>132012912</v>
       </c>
       <c r="B15" t="n">
-        <v>96644</v>
+        <v>57911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>320970</v>
+        <v>321109</v>
       </c>
       <c r="R15" t="n">
-        <v>6432204</v>
+        <v>6432420</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,27 +2220,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stööre kudde 30×40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,53 +2262,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132012912</v>
+        <v>132010885</v>
       </c>
       <c r="B16" t="n">
-        <v>57911</v>
+        <v>96644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321109</v>
+        <v>320970</v>
       </c>
       <c r="R16" t="n">
-        <v>6432420</v>
+        <v>6432204</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2332,22 +2327,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stööre kudde 30×40</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -1831,7 +1831,7 @@
         <v>131917439</v>
       </c>
       <c r="B12" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>132009630</v>
       </c>
       <c r="B14" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>132010885</v>
       </c>
       <c r="B15" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124755299</v>
+        <v>132006673</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320768</v>
+        <v>320750</v>
       </c>
       <c r="R2" t="n">
-        <v>6432130</v>
+        <v>6432190</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>Flera kuddar varav den största ca 40cm diameter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,58 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754215</v>
+        <v>132009630</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320805</v>
+        <v>320875</v>
       </c>
       <c r="R3" t="n">
-        <v>6432195</v>
+        <v>6432213</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,22 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor kudde mes blåmossa, ca 40x60cm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,77 +887,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124755468</v>
+        <v>132010885</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320972</v>
+        <v>320970</v>
       </c>
       <c r="R4" t="n">
-        <v>6432197</v>
+        <v>6432204</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,17 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre spår av födosökande spillkråka</t>
+          <t>Stööre kudde 30×40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879118</v>
+        <v>132006799</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>97810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,45 +1022,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320897</v>
+        <v>320810</v>
       </c>
       <c r="R5" t="n">
-        <v>6432269</v>
+        <v>6432067</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1076,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1106,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124502379</v>
+        <v>124754215</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,23 +1151,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320975</v>
+        <v>320805</v>
       </c>
       <c r="R6" t="n">
-        <v>6432251</v>
+        <v>6432195</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,22 +1191,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124755006</v>
+        <v>124755299</v>
       </c>
       <c r="B7" t="n">
-        <v>56843</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1300,7 +1270,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1310,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>320828</v>
+        <v>320768</v>
       </c>
       <c r="R7" t="n">
-        <v>6432213</v>
+        <v>6432130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124755376</v>
+        <v>124755468</v>
       </c>
       <c r="B8" t="n">
-        <v>56843</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,7 +1384,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1424,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320790</v>
+        <v>320972</v>
       </c>
       <c r="R8" t="n">
-        <v>6432140</v>
+        <v>6432197</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1434,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
+          <t>Äldre spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124755096</v>
+        <v>132009686</v>
       </c>
       <c r="B9" t="n">
-        <v>56843</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,49 +1472,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>320800</v>
+        <v>320890</v>
       </c>
       <c r="R9" t="n">
-        <v>6432124</v>
+        <v>6432241</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,17 +1531,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124877800</v>
+        <v>132011429</v>
       </c>
       <c r="B10" t="n">
-        <v>56843</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,49 +1584,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321049</v>
+        <v>320970</v>
       </c>
       <c r="R10" t="n">
-        <v>6432311</v>
+        <v>6432204</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,12 +1643,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,22 +1673,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124755223</v>
+        <v>132012912</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,46 +1696,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320785</v>
+        <v>321109</v>
       </c>
       <c r="R11" t="n">
-        <v>6432135</v>
+        <v>6432420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,17 +1755,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131917439</v>
+        <v>124502379</v>
       </c>
       <c r="B12" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,20 +1830,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ranebo, Boh</t>
+          <t>Holmevattnet, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>320830</v>
+        <v>320975</v>
       </c>
       <c r="R12" t="n">
-        <v>6432232</v>
+        <v>6432251</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,12 +1870,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,19 +1900,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131917572</v>
+        <v>124754293</v>
       </c>
       <c r="B13" t="n">
         <v>57141</v>
@@ -1966,20 +1945,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ranebo, Boh</t>
+          <t>Svartedalen 1, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321033</v>
+        <v>321004</v>
       </c>
       <c r="R13" t="n">
-        <v>6432350</v>
+        <v>6432367</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2006,12 +1985,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,22 +2020,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132009630</v>
+        <v>124755006</v>
       </c>
       <c r="B14" t="n">
-        <v>96708</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,37 +2043,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartedalen, Svartedalen, Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>320875</v>
+        <v>320828</v>
       </c>
       <c r="R14" t="n">
         <v>6432213</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,27 +2109,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Stor kudde mes blåmossa, ca 40x60cm</t>
+          <t>Spillning på häll i lämplig biotop, rikligt med blåbärsris i markskiktet, nära angränsande mosseskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132010885</v>
+        <v>124755096</v>
       </c>
       <c r="B15" t="n">
-        <v>96708</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,37 +2157,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartedalen, Svartedalen, Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>320970</v>
+        <v>320800</v>
       </c>
       <c r="R15" t="n">
-        <v>6432204</v>
+        <v>6432124</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,27 +2223,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stööre kudde 30×40</t>
+          <t>I lämplig biotop, mycket blåbärsris i marksiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,50 +2260,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132012912</v>
+        <v>124755223</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartedalen, Svartedalen, Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321109</v>
+        <v>320785</v>
       </c>
       <c r="R16" t="n">
-        <v>6432420</v>
+        <v>6432135</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,22 +2337,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:47</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I lämplig biotop, på häll. Rikt med blåbär i markskiktet, o angränsande mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,53 +2374,60 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132009686</v>
+        <v>124755376</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartedalen, Svartedalen, Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>320890</v>
+        <v>320790</v>
       </c>
       <c r="R17" t="n">
-        <v>6432241</v>
+        <v>6432140</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2444,22 +2451,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning efter Tjäder i lämplig miljö, nedan häll. Rikt med blåbärsris i markskiktet och nära mosse/mosseskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,53 +2488,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132011429</v>
+        <v>124877800</v>
       </c>
       <c r="B18" t="n">
-        <v>57951</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartedalen, Svartedalen, Boh</t>
+          <t>Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>320970</v>
+        <v>321049</v>
       </c>
       <c r="R18" t="n">
-        <v>6432204</v>
+        <v>6432311</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2556,22 +2565,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,15 +2585,872 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124879054</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>320897</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6432269</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131917531</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>320979</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6432355</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131917572</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>321033</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6432350</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131917584</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>321004</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6432356</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131917661</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>321001</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6432365</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132006116</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svartedalen, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>320810</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6432067</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Medelfärsk spillning på hällmark</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131917439</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>320830</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6432232</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131917386</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>320864</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6432157</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3349,10 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131917386</v>
+        <v>135321944</v>
       </c>
       <c r="B26" t="n">
-        <v>56706</v>
+        <v>58136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3360,45 +3360,56 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206046</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ranebo, Boh</t>
+          <t>Nedre Långevatten, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>320864</v>
+        <v>320754</v>
       </c>
       <c r="R26" t="n">
-        <v>6432157</v>
+        <v>6432145</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3422,12 +3433,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,15 +3463,120 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131917386</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>320864</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6432157</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Liv Vikingson</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132006799</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132006116</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132006673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132009630</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132010885</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754215</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124755299</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124755468</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132009686</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011429</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1906,6 +1961,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132012912</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2021,6 +2081,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124502379</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2141,6 +2206,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754293</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124755006</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2369,6 +2444,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124755096</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124755223</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2597,6 +2682,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124755376</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2706,6 +2796,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124877800</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2821,6 +2916,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879054</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2926,6 +3026,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131917531</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3031,6 +3136,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131917572</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3136,6 +3246,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131917584</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3241,6 +3356,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131917661</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3346,6 +3466,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131917439</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3472,6 +3597,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321944</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3577,8 +3707,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131917386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -3477,7 +3477,7 @@
         <v>135321944</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 13912-2025 artfynd.xlsx
+++ b/artfynd/A 13912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,10 +3474,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131917386</v>
+        <v>135321944</v>
       </c>
       <c r="B26" t="n">
-        <v>56706</v>
+        <v>58141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3485,45 +3485,56 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206046</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ranebo, Boh</t>
+          <t>Nedre Långevatten, Svartedalen (Stenungsunds kommun), Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>320864</v>
+        <v>320754</v>
       </c>
       <c r="R26" t="n">
-        <v>6432157</v>
+        <v>6432145</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3547,12 +3558,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3567,16 +3588,126 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Boel Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Boel Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321944</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131917386</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>320864</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6432157</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131917386</t>
         </is>
@@ -3609,6 +3740,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
